--- a/ig/ch-core/StructureDefinition-ch-core-medicationrequest.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2353" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2388" uniqueCount="486">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -435,38 +435,65 @@
     <t>MedicationRequest.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -1168,6 +1195,9 @@
     <t>MedicationRequest.dispenseRequest.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
@@ -1406,9 +1436,6 @@
   <si>
     <t xml:space="preserve">type:$this}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>code</t>
@@ -1823,7 +1850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO63"/>
+  <dimension ref="A1:AO64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.92578125" customWidth="true" bestFit="true"/>
@@ -2817,7 +2844,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2836,17 +2863,15 @@
         <v>83</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>83</v>
@@ -2883,16 +2908,14 @@
         <v>83</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>141</v>
@@ -2916,7 +2939,7 @@
         <v>83</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>83</v>
@@ -2930,43 +2953,41 @@
         <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>83</v>
       </c>
@@ -3014,7 +3035,7 @@
         <v>83</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -3023,7 +3044,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>142</v>
@@ -3046,14 +3067,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3066,24 +3087,26 @@
         <v>83</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>83</v>
       </c>
@@ -3131,7 +3154,7 @@
         <v>83</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3143,30 +3166,30 @@
         <v>83</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>153</v>
+        <v>83</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>157</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3174,31 +3197,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3224,13 +3247,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>162</v>
+        <v>83</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3248,13 +3271,13 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>83</v>
@@ -3263,27 +3286,27 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3291,7 +3314,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>91</v>
@@ -3300,22 +3323,22 @@
         <v>83</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3341,13 +3364,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -3365,10 +3388,10 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>91</v>
@@ -3380,16 +3403,16 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>83</v>
@@ -3397,10 +3420,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3408,7 +3431,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>91</v>
@@ -3417,22 +3440,22 @@
         <v>83</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3458,7 +3481,7 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="Y14" t="s" s="2">
         <v>183</v>
@@ -3482,10 +3505,10 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>91</v>
@@ -3506,7 +3529,7 @@
         <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>83</v>
@@ -3514,10 +3537,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3525,31 +3548,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3575,14 +3598,14 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z15" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
@@ -3599,13 +3622,13 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>83</v>
@@ -3614,16 +3637,16 @@
         <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>83</v>
@@ -3645,7 +3668,7 @@
         <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3654,10 +3677,10 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>197</v>
@@ -3665,7 +3688,9 @@
       <c r="M16" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3690,13 +3715,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3720,7 +3745,7 @@
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3729,16 +3754,16 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -3766,23 +3791,21 @@
         <v>83</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3807,13 +3830,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>170</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -3846,16 +3869,16 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -3863,10 +3886,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3883,21 +3906,23 @@
         <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
@@ -3946,7 +3971,7 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3967,7 +3992,7 @@
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>83</v>
@@ -3978,10 +4003,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3989,7 +4014,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>91</v>
@@ -4004,17 +4029,15 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4039,13 +4062,13 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>220</v>
+        <v>83</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>221</v>
+        <v>83</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
@@ -4063,10 +4086,10 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>91</v>
@@ -4078,27 +4101,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4121,16 +4144,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4156,13 +4179,13 @@
         <v>83</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>83</v>
+        <v>229</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>83</v>
@@ -4180,7 +4203,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>91</v>
@@ -4195,27 +4218,27 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>236</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4223,7 +4246,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>91</v>
@@ -4235,19 +4258,19 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4297,10 +4320,10 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>91</v>
@@ -4312,27 +4335,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4343,7 +4366,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4355,15 +4378,17 @@
         <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4412,13 +4437,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4430,24 +4455,24 @@
         <v>250</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>251</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>83</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4458,7 +4483,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4467,16 +4492,16 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4527,13 +4552,13 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
@@ -4542,27 +4567,27 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>257</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>260</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4585,13 +4610,13 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4642,7 +4667,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4657,27 +4682,27 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AM24" t="s" s="2">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>83</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4697,16 +4722,16 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4757,7 +4782,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4772,16 +4797,16 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4789,10 +4814,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4812,20 +4837,18 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>276</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4850,13 +4873,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -4874,7 +4897,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4889,16 +4912,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -4929,18 +4952,20 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -4965,13 +4990,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>83</v>
+        <v>286</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5004,16 +5029,16 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5021,10 +5046,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5035,7 +5060,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5047,17 +5072,15 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5082,13 +5105,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>292</v>
+        <v>83</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>293</v>
+        <v>83</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5106,13 +5129,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5121,27 +5144,27 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AO28" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5164,16 +5187,16 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>178</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5199,13 +5222,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>301</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5223,7 +5246,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5238,27 +5261,27 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL29" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN29" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="AO29" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5278,18 +5301,20 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5338,7 +5363,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5353,16 +5378,16 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5370,10 +5395,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5396,13 +5421,13 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>105</v>
+        <v>315</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5453,7 +5478,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5468,13 +5493,13 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>83</v>
@@ -5485,10 +5510,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5511,13 +5536,13 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5568,7 +5593,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5583,13 +5608,13 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>83</v>
@@ -5600,10 +5625,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5614,7 +5639,7 @@
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5626,18 +5651,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>149</v>
+        <v>324</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>324</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5685,13 +5708,13 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
@@ -5700,13 +5723,13 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>83</v>
@@ -5717,10 +5740,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5740,21 +5763,21 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -5778,13 +5801,13 @@
         <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -5802,7 +5825,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5817,13 +5840,13 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>83</v>
@@ -5834,10 +5857,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5848,7 +5871,7 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -5860,7 +5883,7 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>335</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>336</v>
@@ -5868,7 +5891,9 @@
       <c r="M35" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -5893,13 +5918,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -5917,13 +5942,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -5932,13 +5957,13 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>83</v>
@@ -5949,10 +5974,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5975,13 +6000,13 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6032,7 +6057,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6047,13 +6072,13 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>83</v>
@@ -6064,10 +6089,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6090,17 +6115,15 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N37" t="s" s="2">
         <v>351</v>
       </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6149,7 +6172,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6167,10 +6190,10 @@
         <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>83</v>
@@ -6181,10 +6204,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6195,7 +6218,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6207,15 +6230,17 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6264,13 +6289,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6279,13 +6304,13 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>83</v>
@@ -6296,10 +6321,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6322,13 +6347,13 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6379,7 +6404,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6391,16 +6416,16 @@
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>366</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>83</v>
@@ -6411,21 +6436,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6437,17 +6462,15 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>138</v>
+        <v>370</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6496,19 +6519,19 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>83</v>
@@ -6517,7 +6540,7 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>83</v>
@@ -6528,14 +6551,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6548,26 +6571,24 @@
         <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6615,7 +6636,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6636,7 +6657,7 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>83</v>
@@ -6647,44 +6668,46 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>355</v>
+        <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -6732,19 +6755,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6753,7 +6776,7 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>378</v>
+        <v>134</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>83</v>
@@ -6764,10 +6787,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6790,15 +6813,17 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -6847,7 +6872,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6859,7 +6884,7 @@
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -6868,7 +6893,7 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>83</v>
@@ -6879,21 +6904,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -6905,17 +6930,15 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>138</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -6964,19 +6987,19 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -6985,7 +7008,7 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>83</v>
@@ -6996,14 +7019,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7016,26 +7039,24 @@
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7083,7 +7104,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7104,7 +7125,7 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>83</v>
@@ -7115,42 +7136,46 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>383</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7204,13 +7229,13 @@
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7219,7 +7244,7 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>386</v>
+        <v>134</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>83</v>
@@ -7230,10 +7255,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7256,13 +7281,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7313,7 +7338,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7334,7 +7359,7 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>83</v>
@@ -7345,10 +7370,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7371,13 +7396,13 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7428,7 +7453,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7449,7 +7474,7 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>83</v>
@@ -7460,10 +7485,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7486,20 +7511,16 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7547,7 +7568,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7565,10 +7586,10 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>83</v>
@@ -7579,10 +7600,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7605,18 +7626,20 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7664,7 +7687,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7682,24 +7705,24 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7722,15 +7745,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>383</v>
+        <v>413</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -7779,7 +7804,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7797,24 +7822,24 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7837,17 +7862,15 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -7896,7 +7919,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7914,24 +7937,24 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7954,15 +7977,17 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>424</v>
+        <v>397</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8011,7 +8036,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8029,13 +8054,13 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>287</v>
+        <v>83</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8043,10 +8068,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8069,13 +8094,13 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8126,7 +8151,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8144,13 +8169,13 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>431</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8158,10 +8183,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8184,13 +8209,13 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>362</v>
+        <v>438</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>363</v>
+        <v>439</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8241,7 +8266,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>437</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8253,16 +8278,16 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>83</v>
+        <v>440</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>365</v>
+        <v>441</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>83</v>
@@ -8273,21 +8298,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -8299,17 +8324,15 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>138</v>
+        <v>370</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8358,19 +8381,19 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
@@ -8379,7 +8402,7 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>83</v>
@@ -8390,14 +8413,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>370</v>
+        <v>150</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8410,26 +8433,24 @@
         <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8477,7 +8498,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8498,7 +8519,7 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>134</v>
+        <v>373</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>83</v>
@@ -8509,44 +8530,46 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>437</v>
+        <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>438</v>
+        <v>380</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -8570,74 +8593,74 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>441</v>
+        <v>83</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>436</v>
+        <v>382</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>431</v>
+        <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>445</v>
+        <v>134</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>91</v>
@@ -8652,16 +8675,16 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>170</v>
+        <v>446</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8687,29 +8710,29 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y59" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="Z59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>91</v>
@@ -8727,26 +8750,28 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
       </c>
@@ -8767,15 +8792,17 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -8800,13 +8827,11 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -8824,10 +8849,10 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>91</v>
@@ -8842,16 +8867,16 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="61">
@@ -8882,13 +8907,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8915,13 +8940,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>83</v>
+        <v>182</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>83</v>
+        <v>462</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -8954,38 +8979,38 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>462</v>
+        <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -8997,17 +9022,15 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N62" t="s" s="2">
         <v>469</v>
       </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9056,13 +9079,13 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
@@ -9071,13 +9094,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>83</v>
@@ -9088,14 +9111,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>83</v>
+        <v>473</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9114,16 +9137,16 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9173,7 +9196,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9188,18 +9211,135 @@
         <v>103</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>83</v>
       </c>
     </row>
